--- a/public/exports-60-250-with-coowners/29188599.xlsx
+++ b/public/exports-60-250-with-coowners/29188599.xlsx
@@ -10939,7 +10939,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
